--- a/vse-loti/339373171/spec-339373171.xlsx
+++ b/vse-loti/339373171/spec-339373171.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +441,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +512,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,45 +520,45 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>2018347.65</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>2422017.18</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>2018347.65</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>2018347.65</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>2422017.18</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="6" t="n">
         <v>2018347.65</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="6" t="n">
         <v>2119265.03</v>
       </c>
     </row>

--- a/vse-loti/339373171/spec-339373171.xlsx
+++ b/vse-loti/339373171/spec-339373171.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -69,7 +69,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -509,35 +508,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Трубы стальные бесшовные горячедеформированные</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>2018347.65</v>
+        <v>12232.41</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2422017.18</v>
+        <v>14678.89</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>2018347.65</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>2018347.65</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>2422017.18</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -545,10 +538,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="5" t="n">
         <v>2018347.65</v>
       </c>
     </row>
@@ -558,7 +548,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="5" t="n">
         <v>2119265.03</v>
       </c>
     </row>

--- a/vse-loti/339373171/spec-339373171.xlsx
+++ b/vse-loti/339373171/spec-339373171.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,10 +65,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,8 +445,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +475,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -521,16 +508,10 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>12232.41</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>14678.89</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>2018347.65</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -538,7 +519,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>2018347.65</v>
       </c>
     </row>
@@ -548,14 +529,14 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>2119265.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Источник: Ч. 4 Обоснование НМЦ.xlsx</t>
+          <t>Источник: Ч. 2 Техническое задание.docx</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339373171/spec-339373171.xlsx
+++ b/vse-loti/339373171/spec-339373171.xlsx
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,12 +30,18 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,7 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,15 +71,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,17 +459,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,35 +481,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -495,48 +526,106 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Трубы стальные бесшовные горячедеформированные</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+          <t>Электросварная труба Ду 630×10, марка стали Ст20</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>630×10</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>165</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
+        <v>25.229</v>
+      </c>
+      <c r="G2" s="6" t="n">
         <v>2018347.65</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" s="6" t="n">
+        <v>80002.62</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>96003.14</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="9" t="n">
+        <v>25.229</v>
+      </c>
+      <c r="G3" s="10" t="n">
         <v>2018347.65</v>
       </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>2119265.03</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Источник: Ч. 2 Техническое задание.docx</t>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2018347.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС):</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2422017.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Источник 1 (ТЗ, D, s, марка стали): Ч. 2 Техническое задание.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Источник 2 (НМЦД, цена за метр): Ч. 4 Обоснование НМЦ.xlsx, протокол №290 от 07.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Примечание: кол-во в ТЗ — в метрах; масса приведена по теоретической массе 1 м (ГОСТ 10704 для 630×10 ≈ 152.9 кг/м).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Цена за метр без НДС (минимальная по 3 КП): 12 232.40 ₽/м. Цены КП: ИП Рухлаев 12 232.40; АО Загорский ТЗ 25 606.60; АО ВМЗ 16 461.70.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>ОКПД2: 24.20.13.130 (трубы стальные электросварные). Марка стали Ст20.</t>
         </is>
       </c>
     </row>
